--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2644,6 +2644,327 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128833402</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567081</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6434077</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128833169</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567115</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6434121</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128833226</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567115</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6434121</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,6 +2964,545 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128887153</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567075</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6434046</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128887188</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567075</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6434046</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128887141</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57557</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567075</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6434046</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sedd o hörd. Väldigt liv på småfåglar gjorde att jag visslade, Ganska direkt svarade den och sågs sedan i flera grantoppar.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128887062</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105688</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567102</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6434053</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128886697</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>567111</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6434106</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3504,6 +3504,106 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128905415</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5449</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 39298, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567084</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6434049</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,39 +2967,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>58086</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3076,35 +3072,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B23" t="n">
-        <v>58086</v>
+        <v>57876</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,35 +2967,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>58086</v>
+        <v>57876</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3072,39 +3076,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>58086</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128833169</v>
       </c>
       <c r="B20" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>128887141</v>
       </c>
       <c r="B24" t="n">
-        <v>57557</v>
+        <v>57561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>128886697</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,39 +2967,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B22" t="n">
-        <v>57880</v>
+        <v>58090</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3076,35 +3072,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B23" t="n">
-        <v>58090</v>
+        <v>57880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128833169</v>
       </c>
       <c r="B20" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,35 +2967,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>58090</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3072,39 +3076,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>57880</v>
+        <v>58093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -3184,7 +3184,7 @@
         <v>128887141</v>
       </c>
       <c r="B24" t="n">
-        <v>57561</v>
+        <v>57564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>128886697</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>128886697</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,35 +2967,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>58093</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3072,39 +3076,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>58093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128833169</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>128887141</v>
       </c>
       <c r="B24" t="n">
-        <v>57564</v>
+        <v>57566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>128886697</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,39 +2967,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>58095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3076,35 +3072,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B23" t="n">
-        <v>58095</v>
+        <v>57885</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128833169</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,35 +2967,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>58095</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3072,39 +3076,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>57885</v>
+        <v>58097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -3184,7 +3184,7 @@
         <v>128887141</v>
       </c>
       <c r="B24" t="n">
-        <v>57566</v>
+        <v>57568</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>128886697</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92864</v>
+        <v>92850</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,39 +2967,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3076,35 +3072,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92850</v>
+        <v>92851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,9 +3519,14 @@
       <c r="E27" t="n">
         <v>5449</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
+          <t>Phellodon niger s.lat.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2649,7 +2649,7 @@
         <v>128833402</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128833226</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,35 +2967,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B22" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3072,39 +3076,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>128887062</v>
       </c>
       <c r="B25" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>128886697</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92851</v>
+        <v>92854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -2967,39 +2967,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128887153</v>
+        <v>128887188</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -3076,35 +3072,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128887188</v>
+        <v>128887153</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3509,7 +3509,7 @@
         <v>128905415</v>
       </c>
       <c r="B27" t="n">
-        <v>92854</v>
+        <v>92856</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3614,7 +3614,7 @@
         <v>130450180</v>
       </c>
       <c r="B28" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91785</v>
+        <v>91788</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83143</v>
+        <v>83146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B33" t="n">
-        <v>96362</v>
+        <v>92150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R33" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,8 +4176,14 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4194,32 +4200,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B34" t="n">
-        <v>92147</v>
+        <v>96365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4229,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R34" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,14 +4279,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83141</v>
+        <v>83144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3614,7 +3614,7 @@
         <v>130450180</v>
       </c>
       <c r="B28" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91788</v>
+        <v>91814</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83146</v>
+        <v>83172</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>92150</v>
+        <v>96391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R33" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,14 +4176,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4200,32 +4194,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>96365</v>
+        <v>92176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4235,10 +4229,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R34" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,8 +4273,14 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83144</v>
+        <v>83170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91814</v>
+        <v>91815</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83172</v>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>96391</v>
+        <v>96392</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>92176</v>
+        <v>92177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83170</v>
+        <v>83171</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91815</v>
+        <v>91816</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>96392</v>
+        <v>96393</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83171</v>
+        <v>83172</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3614,7 +3614,7 @@
         <v>130450180</v>
       </c>
       <c r="B28" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83174</v>
+        <v>83176</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>96393</v>
+        <v>96395</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>92178</v>
+        <v>92180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83172</v>
+        <v>83174</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B33" t="n">
-        <v>96395</v>
+        <v>92180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R33" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,8 +4176,14 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4194,32 +4200,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B34" t="n">
-        <v>92180</v>
+        <v>96399</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4229,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R34" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,14 +4279,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>92180</v>
+        <v>96399</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R33" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,14 +4176,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4200,32 +4194,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>96399</v>
+        <v>92180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4235,10 +4229,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R34" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,8 +4273,14 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B33" t="n">
-        <v>96399</v>
+        <v>92180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R33" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,8 +4176,14 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4194,32 +4200,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B34" t="n">
-        <v>92180</v>
+        <v>96399</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4229,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R34" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,14 +4279,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3614,7 +3614,7 @@
         <v>130450180</v>
       </c>
       <c r="B28" t="n">
-        <v>75317</v>
+        <v>75325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91818</v>
+        <v>91831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83176</v>
+        <v>83184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>130450190</v>
       </c>
       <c r="B33" t="n">
-        <v>92180</v>
+        <v>92193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>130450220</v>
       </c>
       <c r="B34" t="n">
-        <v>96399</v>
+        <v>96412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97239</v>
+        <v>97252</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83174</v>
+        <v>83182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3614,7 +3614,7 @@
         <v>130450180</v>
       </c>
       <c r="B28" t="n">
-        <v>75325</v>
+        <v>75326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91831</v>
+        <v>91832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83184</v>
+        <v>83185</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>130450190</v>
       </c>
       <c r="B33" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>130450220</v>
       </c>
       <c r="B34" t="n">
-        <v>96412</v>
+        <v>96413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97252</v>
+        <v>97253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3614,7 +3614,7 @@
         <v>130450180</v>
       </c>
       <c r="B28" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>91833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>130450166</v>
       </c>
       <c r="B32" t="n">
-        <v>83185</v>
+        <v>83186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>92194</v>
+        <v>96416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R33" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,14 +4176,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4200,32 +4194,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>96413</v>
+        <v>92195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4235,10 +4229,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R34" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,8 +4273,14 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97253</v>
+        <v>97256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>130450194</v>
       </c>
       <c r="B36" t="n">
-        <v>83183</v>
+        <v>83184</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -3711,7 +3711,7 @@
         <v>130450086</v>
       </c>
       <c r="B29" t="n">
-        <v>91739</v>
+        <v>91747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>130450079</v>
       </c>
       <c r="B30" t="n">
-        <v>97220</v>
+        <v>97229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>130450267</v>
       </c>
       <c r="B31" t="n">
-        <v>91833</v>
+        <v>91841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>130450220</v>
       </c>
       <c r="B33" t="n">
-        <v>96416</v>
+        <v>96425</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>130450190</v>
       </c>
       <c r="B34" t="n">
-        <v>92195</v>
+        <v>92203</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>130450164</v>
       </c>
       <c r="B35" t="n">
-        <v>97256</v>
+        <v>97265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>130450090</v>
       </c>
       <c r="B37" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 39298-2024 artfynd.xlsx
+++ b/artfynd/A 39298-2024 artfynd.xlsx
@@ -4097,32 +4097,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130450220</v>
+        <v>130450190</v>
       </c>
       <c r="B33" t="n">
-        <v>96425</v>
+        <v>92203</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>6040186</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567198</v>
+        <v>567096</v>
       </c>
       <c r="R33" t="n">
-        <v>6434166</v>
+        <v>6434091</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,8 +4176,14 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4194,32 +4200,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130450190</v>
+        <v>130450220</v>
       </c>
       <c r="B34" t="n">
-        <v>92203</v>
+        <v>96425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>210</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4229,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567096</v>
+        <v>567198</v>
       </c>
       <c r="R34" t="n">
-        <v>6434091</v>
+        <v>6434166</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,14 +4279,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
